--- a/inst/extdata/ploswater.xlsx
+++ b/inst/extdata/ploswater.xlsx
@@ -2297,10 +2297,10 @@
     <t xml:space="preserve">https://orcid.org/0000-0002-3478-2624</t>
   </si>
   <si>
-    <t xml:space="preserve">All the data used in this study are public, except the Pléiades imagery that are commercial. The Pléiades images (Pléiades © CNES 2021 Distribution AIRBUS DS) were licensed to CESBIO by Airbus. The Pléiades DEM is a derivative product subject to the CC-BY-NC 4.0 license preventing commercial use, https://creativecommons.org/licenses/by-nc/4.0/legalcode. We have publicly shared the Digital Elevation Model and derived variables on Zenodo with restricted access until the publication of the manuscript. If needed for the review, you can access to these data-sets by using these links: - 2m resolution DEM based stereoscopy Pleiades acquisitions in Telangana, South-India https://zenodo.org/records/10403040?token=[removed] - Subsample of the maximum Water Area Extent of Telangana Rainwater Harvesting System from Sentinel-2 https://zenodo.org/records/10402199?token=[removed] - Subsample of the maximum Water Area Extent of Telangana Rainwater Harvesting System from Pléiades DEM https://zenodo.org/records/10402355?token=[removed] - Maximum Water Area Extent of the Rainwater Harvesting System in Telangana from GSW https://zenodo.org/records/10402096?token=[removed]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://creativecommons.org/licenses/by-nc/4.0/legalcode; https://zenodo.org/records/10403040?token=[removed]; https://zenodo.org/records/10402199?token=[removed]; https://zenodo.org/records/10402355?token=[removed]; https://zenodo.org/records/10402096?token=[removed]</t>
+    <t xml:space="preserve">All the data used in this study are public, except the Pléiades imagery that are commercial. The Pléiades images (Pléiades © CNES 2021 Distribution AIRBUS DS) were licensed to CESBIO by Airbus. The Pléiades DEM is a derivative product subject to the CC-BY-NC 4.0 license preventing commercial use, https://creativecommons.org/licenses/by-nc/4.0/legalcode. We have publicly shared the Digital Elevation Model and derived variables on Zenodo with restricted access until the publication of the manuscript. If needed for the review, you can access to these data-sets by using these links: - 2m resolution DEM based stereoscopy Pleiades acquisitions in Telangana, South-India https://zenodo.org/records/10403040 - Subsample of the maximum Water Area Extent of Telangana Rainwater Harvesting System from Sentinel-2 https://zenodo.org/records/10402199 - Subsample of the maximum Water Area Extent of Telangana Rainwater Harvesting System from Pléiades DEM https://zenodo.org/records/10402355 - Maximum Water Area Extent of the Rainwater Harvesting System in Telangana from GSW https://zenodo.org/records/10402096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://creativecommons.org/licenses/by-nc/4.0/legalcode; https://zenodo.org/records/10403040; https://zenodo.org/records/10402199; https://zenodo.org/records/10402355; https://zenodo.org/records/10402096</t>
   </si>
   <si>
     <t xml:space="preserve">/Biology and life sciences/Agriculture/Agricultural methods/Agricultural irrigation/Lift irrigation; /Earth sciences/Atmospheric science/Atmospheric physics/Atmospheric dynamics/Atmospheric clouds; /Earth sciences/Geophysics/Atmospheric physics/Atmospheric dynamics/Atmospheric clouds; /Earth sciences/Hydrology/Surface water; /Earth sciences/Marine and aquatic sciences/Aquatic environments/Freshwater environments/Rivers; /Earth sciences/Marine and aquatic sciences/Bodies of water/Rivers; /Ecology and environmental sciences/Aquatic environments/Freshwater environments/Rivers; /Engineering and technology/Remote sensing/Lidar; /Engineering and technology/Remote sensing/Radar; /People and places/Geographical locations/Asia/India; /Physical sciences/Physics/Geophysics/Atmospheric physics/Atmospheric dynamics/Atmospheric clouds; /Physical sciences/Physics/Particle physics/Elementary particles/Photons</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">https://orcid.org/0000-0002-2165-5239</t>
   </si>
   <si>
-    <t xml:space="preserve">The JULES simulation data can be accessed at doi:10.5281/zenodo.10459886. The MERIT DEM [45] is accessible online (https://hydro.iis.utokyo. ac.jp/~yamadai/MERIT_DEM/, last access: 14 December 2023). The HESS [19,20] product is available online (https://daac.ornl.gov/LBA/guides/LC07_Amazon_Wetlands.html, last access: 15 May 2024). The GIEMS [10,40] product can be acquired by contacting Catherine Prigent ([email removed]@obspm.fr). The SWAMPS-GLWD [41] product can be acquired by contacting Zhen Zhang ([email removed]@itpcas.ac.cn). The WAD2M [43] product is available online (https://zenodo.org/records/3998454, last access: 15 May 2024). The WFDEI [48] dataset is available from the ftp site at IIASA, Vienna (ftp.iiasa.ac.at, username: rfdata password: forceDATA, then use: cwd/WFDEI, last access: 15 May 2024). The HELIX [37] data can be acquired by contacting John Ceasar ([email removed]@metoffice.gov.uk). Upon publication the JULES simulation data can be accessed at doi: 10.5281/zenodo.10459886.</t>
+    <t xml:space="preserve">The JULES simulation data can be accessed at doi:10.5281/zenodo.10459886. The MERIT DEM [45] is accessible online (https://hydro.iis.utokyo. ac.jp/~yamadai/MERIT_DEM/, last access: 14 December 2023). The HESS [19,20] product is available online (https://daac.ornl.gov/LBA/guides/LC07_Amazon_Wetlands.html, last access: 15 May 2024). The GIEMS [10,40] product can be acquired by contacting Catherine Prigent ([email removed]@obspm.fr). The SWAMPS-GLWD [41] product can be acquired by contacting Zhen Zhang ([email removed]@itpcas.ac.cn). The WAD2M [43] product is available online (https://zenodo.org/records/3998454, last access: 15 May 2024). The WFDEI [48] dataset is available from the ftp site at IIASA, Vienna (ftp.iiasa.ac.at, username: rfdata password [removed], then use: cwd/WFDEI, last access: 15 May 2024). The HELIX [37] data can be acquired by contacting John Ceasar ([email removed]@metoffice.gov.uk). Upon publication the JULES simulation data can be accessed at doi: 10.5281/zenodo.10459886.</t>
   </si>
   <si>
     <t xml:space="preserve">https://doi.org/10.5281/zenodo.10459886; https://hydro.iis.utokyo; https://daac.ornl.gov/LBA/guides/LC07_Amazon_Wetlands.html; https://zenodo.org/records/3998454; 10.5281/zenodo.10459886</t>
